--- a/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
@@ -1138,7 +1138,7 @@
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Previous event copied
-Given I choose one of my own completed or past events When I copy it Then ConnectSphere creates a new draft with the event requirements and Session structure copied, all event and Session dates/times left blank, and no bookings, reservations, or registrations carried over (assumes O-51)
+Given I choose one of my own completed or past events When I copy it Then ConnectSphere creates a new draft with the event requirements and Session structure copied, all event and Session dates/times left blank, and no bookings, reservations, or registrations carried over (T-99)
 Scenario 2 - Missing reference flagged
 Given the copied event references a venue or equipment item that no longer exists When the draft is created Then the affected requirement is flagged for review and identifies its Session rather than being copied silently
 Scenario 3 - Dates remain subject to current submission policy
@@ -1146,7 +1146,7 @@
 Checklist
 - Copy one of my own completed or past events into a new draft
 - Confirm requirements and Session structure are copied while event and Session dates/times are blank
-- Confirm bookings, equipment reservations and registrations are not copied (assumes O-51)
+- Confirm bookings, equipment reservations and registrations are not copied (T-99)
 - See unavailable venue/equipment references flagged against the relevant Session
 - Submit a copied draft subject to the current date rules</t>
         </is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>C-74, T-79, T-87, T-90, O-51</t>
+          <t>C-74, T-79, T-87, T-90, T-99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
 Scenario 4 - Concurrent submissions do not overbook
 Given one approved seat remains in a Session or in the combined Event capacity When two registrations are submitted at the same time Then at most one is confirmed against that remaining capacity and any other submission that exceeds capacity is Pending
 Scenario 5 - Waiting list remains event-level
-Given the combined Event capacity is full When an Attendee opens registration Then the existing Event-level waiting-list option is offered where enabled; whether a full individual Session offers a separate waiting list is open under O-50
+Given the combined Event capacity is full When an Attendee opens registration Then the existing Event-level waiting-list option is offered where enabled; a full selected Session follows the Pending decision path and has no separate Session-level waiting list (T-98)
 Scenario 6 - Manual addition allowed within both limits
 Given normal registration is full but both the selected Session and combined Event capacity have room When the Event Organiser manually adds an Attendee Then the registration is created as a distinguishable manual addition (C-58, T-50)
 Scenario 7 - Manual addition blocked at either limit
@@ -3428,7 +3428,7 @@
 - Keep an Attendee over-capacity submission Pending for Organiser review without counting it as an approved seat
 - Recheck both limits when the Organiser approves a Pending registration
 - Prevent concurrent requests from exceeding either limit
-- Offer the Event-level waiting list when combined Event capacity is full; apply O-50 for individual full Sessions
+- Offer the Event-level waiting list when combined Event capacity is full; keep a full selected Session on the Pending decision path with no Session-level waiting list (T-98)
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
+          <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, T-98</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
-Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
+Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added to the Event-level list and told I will be notified when a place is released; no Session-level waiting list is created (T-98)
 Scenario 2 - Released place notified to all
 Given a place is released in an event with a waiting list When the place becomes available Then all waitlisted Attendees are notified and the place is claimed on a first-come, first-served basis
 Scenario 3 - Claimed place leaves the list
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>C-23, T-33, T-46, B-10, O-50</t>
+          <t>C-23, T-33, T-46, B-10, T-98</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -4972,7 +4972,7 @@
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Previous event copied
-Given I choose one of my own completed or past events When I copy it Then ConnectSphere creates a new draft with the event requirements and Session structure copied, all event and Session dates/times left blank, and no bookings, reservations, or registrations carried over (assumes O-51)
+Given I choose one of my own completed or past events When I copy it Then ConnectSphere creates a new draft with the event requirements and Session structure copied, all event and Session dates/times left blank, and no bookings, reservations, or registrations carried over (T-99)
 Scenario 2 - Missing reference flagged
 Given the copied event references a venue or equipment item that no longer exists When the draft is created Then the affected requirement is flagged for review and identifies its Session rather than being copied silently
 Scenario 3 - Dates remain subject to current submission policy
@@ -4980,7 +4980,7 @@
 Checklist
 - Copy one of my own completed or past events into a new draft
 - Confirm requirements and Session structure are copied while event and Session dates/times are blank
-- Confirm bookings, equipment reservations and registrations are not copied (assumes O-51)
+- Confirm bookings, equipment reservations and registrations are not copied (T-99)
 - See unavailable venue/equipment references flagged against the relevant Session
 - Submit a copied draft subject to the current date rules</t>
         </is>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>C-74, T-79, T-87, T-90, O-51</t>
+          <t>C-74, T-79, T-87, T-90, T-99</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -7260,7 +7260,7 @@
 Scenario 4 - Concurrent submissions do not overbook
 Given one approved seat remains in a Session or in the combined Event capacity When two registrations are submitted at the same time Then at most one is confirmed against that remaining capacity and any other submission that exceeds capacity is Pending
 Scenario 5 - Waiting list remains event-level
-Given the combined Event capacity is full When an Attendee opens registration Then the existing Event-level waiting-list option is offered where enabled; whether a full individual Session offers a separate waiting list is open under O-50
+Given the combined Event capacity is full When an Attendee opens registration Then the existing Event-level waiting-list option is offered where enabled; a full selected Session follows the Pending decision path and has no separate Session-level waiting list (T-98)
 Scenario 6 - Manual addition allowed within both limits
 Given normal registration is full but both the selected Session and combined Event capacity have room When the Event Organiser manually adds an Attendee Then the registration is created as a distinguishable manual addition (C-58, T-50)
 Scenario 7 - Manual addition blocked at either limit
@@ -7271,7 +7271,7 @@
 - Keep an Attendee over-capacity submission Pending for Organiser review without counting it as an approved seat
 - Recheck both limits when the Organiser approves a Pending registration
 - Prevent concurrent requests from exceeding either limit
-- Offer the Event-level waiting list when combined Event capacity is full; apply O-50 for individual full Sessions
+- Offer the Event-level waiting list when combined Event capacity is full; keep a full selected Session on the Pending decision path with no Session-level waiting list (T-98)
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
+          <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, T-98</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
-Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
+Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added to the Event-level list and told I will be notified when a place is released; no Session-level waiting list is created (T-98)
 Scenario 2 - Released place notified to all
 Given a place is released in an event with a waiting list When the place becomes available Then all waitlisted Attendees are notified and the place is claimed on a first-come, first-served basis
 Scenario 3 - Claimed place leaves the list
@@ -7382,7 +7382,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>C-23, T-33, T-46, B-10, O-50</t>
+          <t>C-23, T-33, T-46, B-10, T-98</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
@@ -3904,7 +3904,7 @@
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
-Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. Re-estimated to five points on 26 October 2026 at the story owner's request, with the change recorded for teammate review through the estimate PR. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. This is the whole-story estimate, not remaining work or elapsed waiting time. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
 Updated on 23 October 2026, before any work on the story started, to the Week 9 decisions that closed O-24 and O-25; an incomplete story's criteria are updated in place (T-74). T-81 returns a Confirmed event that loses its venue to Planning without cancelling it (C-120), replacing the earlier "status unchanged" default in Scenario 1. C-121 confirms the Scenario 4 notification rule.</t>
         </is>
       </c>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
-Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. Re-estimated to five points on 26 October 2026 at the story owner's request, with the change recorded for teammate review through the estimate PR. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. This is the whole-story estimate, not remaining work or elapsed waiting time. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
 Updated on 23 October 2026, before any work on the story started, to the Week 9 decisions that closed O-24 and O-25; an incomplete story's criteria are updated in place (T-74). T-81 returns a Confirmed event that loses its venue to Planning without cancelling it (C-120), replacing the earlier "status unchanged" default in Scenario 1. C-121 confirms the Scenario 4 notification rule.</t>
         </is>
       </c>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
@@ -3904,7 +3904,7 @@
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
-Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. Re-estimated to five points on 26 October 2026 at the story owner's request, with the change recorded for teammate review through the estimate PR. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. This is the whole-story estimate, not remaining work or elapsed waiting time. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. A five-point re-estimate was proposed on 26 October 2026 at the story owner's request for teammate review. Jira remains at three points until the matching backlog PR merges, then is reconciled to five points. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. T-73 estimates in-flight stories for their remaining work only. Because the criteria changed on 23 October before implementation began, team/PO confirmation is required on whether five points records the revised pre-implementation size and how it is counted for sprint reporting. It is not an agreed estimate of work remaining now, and original commitments and historical estimates must be preserved. Elapsed waiting time is not story-point effort. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
 Updated on 23 October 2026, before any work on the story started, to the Week 9 decisions that closed O-24 and O-25; an incomplete story's criteria are updated in place (T-74). T-81 returns a Confirmed event that loses its venue to Planning without cancelling it (C-120), replacing the earlier "status unchanged" default in Scenario 1. C-121 confirms the Scenario 4 notification rule.</t>
         </is>
       </c>
@@ -7760,7 +7760,7 @@
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
-Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. Re-estimated to five points on 26 October 2026 at the story owner's request, with the change recorded for teammate review through the estimate PR. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. This is the whole-story estimate, not remaining work or elapsed waiting time. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. A five-point re-estimate was proposed on 26 October 2026 at the story owner's request for teammate review. Jira remains at three points until the matching backlog PR merges, then is reconciled to five points. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. T-73 estimates in-flight stories for their remaining work only. Because the criteria changed on 23 October before implementation began, team/PO confirmation is required on whether five points records the revised pre-implementation size and how it is counted for sprint reporting. It is not an agreed estimate of work remaining now, and original commitments and historical estimates must be preserved. Elapsed waiting time is not story-point effort. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
 Updated on 23 October 2026, before any work on the story started, to the Week 9 decisions that closed O-24 and O-25; an incomplete story's criteria are updated in place (T-74). T-81 returns a Confirmed event that loses its venue to Planning without cancelling it (C-120), replacing the earlier "status unchanged" default in Scenario 1. C-121 confirms the Scenario 4 notification rule.</t>
         </is>
       </c>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 261026.xlsx
@@ -3904,7 +3904,7 @@
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
-Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. A five-point re-estimate was proposed on 26 October 2026 at the story owner's request for teammate review. Jira remains at three points until the matching backlog PR merges, then is reconciled to five points. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. T-73 estimates in-flight stories for their remaining work only. Because the criteria changed on 23 October before implementation began, team/PO confirmation is required on whether five points records the revised pre-implementation size and how it is counted for sprint reporting. It is not an agreed estimate of work remaining now, and original commitments and historical estimates must be preserved. Elapsed waiting time is not story-point effort. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
 Updated on 23 October 2026, before any work on the story started, to the Week 9 decisions that closed O-24 and O-25; an incomplete story's criteria are updated in place (T-74). T-81 returns a Confirmed event that loses its venue to Planning without cancelling it (C-120), replacing the earlier "status unchanged" default in Scenario 1. C-121 confirms the Scenario 4 notification rule.</t>
         </is>
       </c>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
-Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The original estimate was three points. A five-point re-estimate was proposed on 26 October 2026 at the story owner's request for teammate review. Jira remains at three points until the matching backlog PR merges, then is reconciled to five points. The four current scenarios include lost-booking context and same-event replacement search, linked replacement requests, explicit cancellation only after confirmation, and effective-change publication/notification timing with integration and rollback testing. T-73 estimates in-flight stories for their remaining work only. Because the criteria changed on 23 October before implementation began, team/PO confirmation is required on whether five points records the revised pre-implementation size and how it is counted for sprint reporting. It is not an agreed estimate of work remaining now, and original commitments and historical estimates must be preserved. Elapsed waiting time is not story-point effort. E05-S06 still owns the unavailability trigger and Confirmed-to-Planning transition; that implementation is not counted again here.
 Updated on 23 October 2026, before any work on the story started, to the Week 9 decisions that closed O-24 and O-25; an incomplete story's criteria are updated in place (T-74). T-81 returns a Confirmed event that loses its venue to Planning without cancelling it (C-120), replacing the earlier "status unchanged" default in Scenario 1. C-121 confirms the Scenario 4 notification rule.</t>
         </is>
       </c>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
